--- a/DOC/基本設計書/ソフトウェア仕様書_別紙2_設定一覧.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_別紙2_設定一覧.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomoki/project/Todo_Java_Swing/DOC/基本設計書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Todo_Java_Swing\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC1233C-0A06-9D41-9AB5-9C11B408D8C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B8D650-9B7D-4AEC-8044-236B1FCEC6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15920" xr2:uid="{8483CCA3-FAB1-9041-83F7-C09BCB54721B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8483CCA3-FAB1-9041-83F7-C09BCB54721B}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
     <sheet name="1_設定ファイル" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'1_設定ファイル'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1_設定ファイル'!$A$1:$G$48</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>シート名</t>
     <phoneticPr fontId="1"/>
@@ -121,38 +121,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DB接続先ホスト</t>
-    <rPh sb="0" eb="2">
-      <t>セツゾクサキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DB接続先ポート番号</t>
-    <rPh sb="0" eb="2">
-      <t>セツゾクサキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DB接続タイムアウト値</t>
-    <rPh sb="0" eb="2">
-      <t>セツゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面更新インターバル値</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DBHostPortNum</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デフォルト値</t>
     <rPh sb="0" eb="1">
       <t>アタイ</t>
@@ -174,64 +142,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>localhost</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クライアント端末から見たMySQLサーバのIPアドレスを設定</t>
-    <rPh sb="0" eb="2">
-      <t>タンマツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0〜65535</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MySQLサーバの待ち受けポート番号を設定</t>
-    <rPh sb="0" eb="1">
-      <t>マチウケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DBAccessTimeout</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0〜600</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DBクエリ実行時のタイムアウト値（秒）を設定
-最大値を10分とし、超過した値を設定した場合は最大値で丸める動作とする。動作保証は10分までとする。</t>
-    <rPh sb="0" eb="2">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0, 60〜600</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DisplayUpdateInterval</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・TODO（Jarファイルに内包するのか？）</t>
     <rPh sb="0" eb="1">
       <t>ニナイホウスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>周期タイマによる画面更新のインターバル値（秒）を設定
-0秒設定の場合は無効とする。
-最大値を10分とし、超過した値を設定した場合は最大値で丸める動作とする。動作保証は10分までとする。</t>
-    <rPh sb="0" eb="2">
-      <t>シュウキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -292,25 +205,146 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DBHostIPAddress</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DBHostIPAddress=localhost
-DBHostPortNum=3306
-DBUserName=test
-DBPassword=P@ssw0rd
-DBName=ToDoDB
-DBAccessTimeout=10
-DisplayUpdateInterval=60</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>DB接続に使用するパスワードを平文で設定
 空文字以外を許容とする。空文字の場合でもデフォルト値は定義せずそのまま処理が継続する動作とするが、動作保証しない。</t>
     <rPh sb="0" eb="2">
       <t>セツゾク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBConnectionString</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB接続文字列</t>
+    <rPh sb="0" eb="2">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB接続文字列を設定
+空文字以外を許容とする。空文字の場合でもデフォルト値は定義せずそのまま処理が継続する動作とするが、動作保証しない。</t>
+    <rPh sb="0" eb="2">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBDriverName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JDBCドライバクラス名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LogRotationSize</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイルのサイズ上限を設定
+空文字以外を許容とする。空文字の場合でもデフォルト値は定義せずそのまま処理が継続する動作とするが、動作保証しない。</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイルサイズ上限</t>
+    <rPh sb="9" eb="11">
+      <t>ジョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BaseUrl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ChatPath</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ModelName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ApiKey</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SystemPrompt</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LM StudioserverURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LM StudioサーバーのベースURL。ChatPathと文字列結合してリクエスト先URLを構成する（url =BaseUrl + ChatPath）。空文字の場合は接続失敗となるが、動作保証しない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャットAPIパス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャット機能のAPIパス。BaseUrlと文字列結合してリクエスト先URLを構成する（url = BaseUrl +ChatPath）。LM StudioはOpenAI互換APIを提供するため、標準ではは/v1/chat/completionsを指定する。空文字の場合はBaseUrlのみがURLとなる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIモデル名</t>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LM Studioでロード中のモデル名。リクエストJSONの model フィールドとして送信される。LM Studio側でロードしているモデル名と完全一致させる必要がある。不一致の場合はAPIエラーとなるが、動作保証しない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIキー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LMStudio接続用のAPIキー。現在の実装ではHTTPリクエストのAuthorizationヘッダには付与されておらず、実質的に未使用。LMStudio自体はAPIキーを必須としないため任意の文字列を設定可能。将来の拡張に備えて設定項目として保持している。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムプロンプト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIへのシステムプロンプト。リクエストJSONの messages 配列内に role: "system"のメッセージとして先頭に付与される。空文字の場合はシステムメッセージが空のまま送信され、AIの応答フォーマットが保証されない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBConnectionString=jdbc:mysql://localhost:3306/todojava_db?connectTimeout=10000&amp;socketTimeout=10000
+DBDriverName=com.mysql.cj.jdbc.Driver
+DBUserName=test
+DBPassword=P@ssw0rd
+DBName=todojava_db
+LogRotationSize=536870912
+BaseUrl=http://192.168.0.10:1234
+ChatPath=/v1/chat/completions
+ModelName=llama-3.2-3b-instruct
+ApiKey=lm-studio
+SystemPrompt=あなたはTodoリストのリスト名とタスクを考えるためのAIです。\
+    質問された内容について、リスト名を1つ作成していただく。\
+    合わせて問題解決や学習、能力取得のためのタスクを必要なだけ箇条書きで回答してください。\
+    タスクは1行でわかる具体的手順で書くこと。\
+    タスクの個数について質問内容に指定がある場合はそれに従うこと。\
+    タスクの生成個数上限は500件とすること。\
+    回答はかならず日本語で回答をしてください。\
+    回答は必ずJSON形式で出力してください。\
+    以下のフォーマットで、余計なテキストを含まずそのまま `JsonParser.parseString()` で読める純粋な JSON オブジェクトを返して下さい。\
+    {  "リスト名": "...",  "タスク": [ "...", "..." ]}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -318,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -358,7 +392,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -398,6 +432,15 @@
         <color indexed="64"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -414,12 +457,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -429,11 +466,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -750,19 +793,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87D99CD-4C20-F24B-9433-B1D69E739214}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -773,7 +816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -787,268 +830,300 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7F4906-62F4-2D4E-BF9D-4EACD53A2029}">
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3306</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="63">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="63">
+        <v>17</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="63">
+        <v>17</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="63">
+        <v>17</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="78" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="4">
-        <v>10</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="84">
+      <c r="F18" s="4"/>
+      <c r="G18" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="58.5" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="2">
-        <v>60</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="97.5" x14ac:dyDescent="0.4">
+      <c r="B20" s="2">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="78" x14ac:dyDescent="0.4">
+      <c r="B21" s="2">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="78" x14ac:dyDescent="0.4">
+      <c r="B22" s="2">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="78" x14ac:dyDescent="0.4">
+      <c r="B23" s="2">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -1056,7 +1131,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -1064,12 +1139,156 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
     </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B23:G30"/>
+    <mergeCell ref="B28:G48"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="39" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>